--- a/Doc/GameExcels/dic_myths.xlsx
+++ b/Doc/GameExcels/dic_myths.xlsx
@@ -1,383 +1,193 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Yijue\Shanhaijing_laya\Doc\GameExcels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17775" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>name_desc</t>
-  </si>
-  <si>
-    <t>lock</t>
-  </si>
-  <si>
-    <t>img</t>
-  </si>
-  <si>
-    <t>definition_info</t>
-  </si>
-  <si>
-    <t>definition_info_desc</t>
-  </si>
-  <si>
-    <t>Original_info</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>海经章节id</t>
-  </si>
-  <si>
-    <t>章节名字，键值</t>
-  </si>
-  <si>
-    <t>备注不读</t>
-  </si>
-  <si>
-    <t>1锁0不锁</t>
-  </si>
-  <si>
-    <t>插画，&amp;链接多图</t>
-  </si>
-  <si>
-    <t>现代释义，填键值</t>
-  </si>
-  <si>
-    <t>原著文本，不参与多语言</t>
-  </si>
-  <si>
-    <t>myths_chapter_1</t>
-  </si>
-  <si>
-    <t>章节名字六字</t>
-  </si>
-  <si>
-    <t>1101&amp;1102&amp;1103&amp;1104&amp;1105</t>
-  </si>
-  <si>
-    <t>definition_myths_info_1</t>
-  </si>
-  <si>
-    <t>第1章现代译文</t>
-  </si>
-  <si>
-    <t>填第1章原著文本</t>
-  </si>
-  <si>
-    <t>myths_chapter_2</t>
-  </si>
-  <si>
-    <t>2101&amp;2102&amp;2103&amp;2104&amp;2105</t>
-  </si>
-  <si>
-    <t>definition_myths_info_2</t>
-  </si>
-  <si>
-    <t>第2章现代译文</t>
-  </si>
-  <si>
-    <t>填第2章原著文本</t>
-  </si>
-  <si>
-    <t>myths_chapter_3</t>
-  </si>
-  <si>
-    <t>3101&amp;3102&amp;3103&amp;3104&amp;3105</t>
-  </si>
-  <si>
-    <t>definition_myths_info_3</t>
-  </si>
-  <si>
-    <t>第3章现代译文</t>
-  </si>
-  <si>
-    <t>填第3章原著文本</t>
-  </si>
-  <si>
-    <t>myths_chapter_4</t>
-  </si>
-  <si>
-    <t>4101&amp;4102&amp;4103&amp;4104&amp;4105</t>
-  </si>
-  <si>
-    <t>definition_myths_info_4</t>
-  </si>
-  <si>
-    <t>第4章现代译文</t>
-  </si>
-  <si>
-    <t>填第4章原著文本</t>
-  </si>
-  <si>
-    <t>myths_chapter_5</t>
-  </si>
-  <si>
-    <t>5101&amp;5102&amp;5103&amp;5104&amp;5105</t>
-  </si>
-  <si>
-    <t>definition_myths_info_5</t>
-  </si>
-  <si>
-    <t>第5章现代译文</t>
-  </si>
-  <si>
-    <t>填第5章原著文本</t>
-  </si>
-  <si>
-    <t>myths_chapter_6</t>
-  </si>
-  <si>
-    <t>6101&amp;6102&amp;6103&amp;6104&amp;6105</t>
-  </si>
-  <si>
-    <t>definition_myths_info_6</t>
-  </si>
-  <si>
-    <t>第6章现代译文</t>
-  </si>
-  <si>
-    <t>填第6章原著文本</t>
-  </si>
-  <si>
-    <t>myths_chapter_7</t>
-  </si>
-  <si>
-    <t>7101&amp;7102&amp;7103&amp;7104&amp;7105</t>
-  </si>
-  <si>
-    <t>definition_myths_info_7</t>
-  </si>
-  <si>
-    <t>第7章现代译文</t>
-  </si>
-  <si>
-    <t>填第7章原著文本</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="36">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -710,176 +520,177 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -933,11 +744,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1189,284 +1063,1558 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="21.125" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="8.875" customWidth="1"/>
-    <col min="5" max="5" width="30.875" customWidth="1"/>
-    <col min="6" max="6" width="23.875" customWidth="1"/>
-    <col min="7" max="7" width="42.875" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col width="11.5" customWidth="1" style="7" min="1" max="1"/>
+    <col width="21.125" customWidth="1" style="7" min="2" max="2"/>
+    <col width="17.625" customWidth="1" style="7" min="3" max="3"/>
+    <col width="8.875" customWidth="1" style="7" min="4" max="4"/>
+    <col width="30.875" customWidth="1" style="7" min="5" max="5"/>
+    <col width="23.875" customWidth="1" style="7" min="6" max="6"/>
+    <col width="42.875" customWidth="1" style="7" min="7" max="7"/>
+    <col width="34" customWidth="1" style="7" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name_desc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>lock</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>img</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>definition_info</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>definition_info_desc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Original_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>海经章节id</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>章节名字，键值</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>备注不读</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1锁0不锁</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>插画，&amp;链接多图</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>现代释义，填键值</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>备注不读</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>原著文本，不参与多语言</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>myths_chapter_1</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>女娲造人</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>definition_myths_info_1</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>第1章现代译文</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>有神十人，名曰女娲之肠，化为神，处栗广之野，横道而处。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>myths_chapter_2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>女娲补天</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>definition_myths_info_2</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>第2章现代译文</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>（淮南子）往古之时，四极废，九州裂，天不兼覆，地不周载……女娲炼五色石以补苍天，断鳌足以立四极，杀黑龙以济冀州，积芦灰以止淫水。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>myths_chapter_3</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>共工触不周山</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>definition_myths_info_3</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>第3章现代译文</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>西北海之外，大荒之隅，有山而不合，名曰不周……共工之臣曰相柳……（淮南子）共工与颛顼争为帝，怒而触不周之山，天柱折，地维绝。天倾西北，故日月星辰移焉；地不满东南，故水潦尘埃归焉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>myths_chapter_4</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>重黎绝地天通</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>definition_myths_info_4</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>第4章现代译文</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>颛顼生老童，老童生重及黎，帝令重献上天，令黎卬下地，下地是生噎，处于西极，以行日月星辰之行次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>myths_chapter_5</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>烛龙司昼夜四时</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>definition_myths_info_5</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>第5章现代译文</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>钟山之神，名曰烛阴，视为昼，瞑为夜，吹为冬，呼为夏，不饮，不食，不息，息为风。身长千里。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>myths_chapter_6</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>羲和浴日（生十日）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>definition_myths_info_6</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>第6章现代译文</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>有女子名曰羲和，方浴日于甘渊。羲和者，帝俊之妻，生十日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>myths_chapter_7</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>常羲浴月（生十二月）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>definition_myths_info_7</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>第7章现代译文</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>有女子方浴月。帝俊妻常羲，生月十有二，此始浴之。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_8</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>十日并出与后羿射日</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_8</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>第8章现代译文</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>（淮南子）逮至尧之时，十日并出，焦禾稼，杀草木，而民无所食……尧乃使羿……上射十日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_9</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>夸父逐日</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_9</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>第9章现代译文</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>夸父与日逐走，入日。渴，欲得饮，饮于河渭；河渭不足，北饮大泽。未至，道渴而死。弃其杖，化为邓林。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="3" t="s">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_10</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>精卫填海</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_10</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>第10章现代译文</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>有鸟焉，其状如乌，文首、白喙、赤足，名曰精卫，其鸣自詨。是炎帝之少女，名曰女娃。女娃游于东海，溺而不返，故为精卫，常衔西山之木石，以堙于东海。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_11</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>鲧禹治水（息壤与父继子承）</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>11101&amp;11102</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_11</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>第11章现代译文</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>洪水滔天。鲧窃帝之息壤以堙洪水，不待帝命。帝令祝融杀鲧于羽郊。鲧复生禹。帝乃命禹卒布土以定九州。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_12</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>应龙助禹杀蚩尤夸父</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_12</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>第12章现代译文</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>应龙处南极，杀蚩尤与夸父，不得复上，故下数旱。旱而为应龙之状，乃得大雨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_13</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>黄帝战蚩尤</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_13</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>第13章现代译文</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>（应龙）杀蚩尤与夸父……（山海经逸文）黄帝乃令应龙攻之冀州之野，蚩尤请风伯雨师，纵大风雨。黄帝乃下天女曰魃，雨止，遂杀蚩尤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_14</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>刑天舞干戚</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_14</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>第14章现代译文</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>刑天与帝至此争神，帝断其首，葬之常羊之山。乃以乳为目，以脐为口，操干戚以舞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_15</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>蚩尤（兵主）</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_15</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>第15章现代译文</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>（宋山）枫木，蚩尤所弃其桎梏，是为枫木……（逸文）蚩尤作兵伐黄帝，黄帝乃令应龙攻之。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_16</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>旱魃（女魃）</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_16</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>第16章现代译文</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>（逸文）有人衣青衣，名曰黄帝女魃。蚩尤作兵伐黄帝……黄帝乃下天女曰魃，雨止，遂杀蚩尤。魃不得复上，所居不雨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_17</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>西王母（司天之厉）</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>17101</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_17</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>第17章现代译文</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>（西山经）西王母其状如人，豹尾虎齿而善啸，蓬发戴胜，是司天之厉及五残。（海外西）西王母居玉山，是司天之厉及五残。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_18</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>四方神（句芒·祝融·蓐收·禺彊）</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>18101&amp;18102&amp;18103&amp;18104</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_18</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>第18章现代译文</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>东方句芒，鸟身人面，乘两龙。南方祝融，兽身人面，乘两龙。西方蓐收，左耳有蛇，乘两龙。北方禺彊，人面鸟身，珥两青蛇，践两青蛇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_19</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>帝俊（上古天帝）</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>19101</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_19</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>第19章现代译文</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>帝俊生中容……帝俊妻羲和，生十日……帝俊妻常羲，生月十有二……帝俊生后稷，稷降以百谷……帝俊竹林……</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_20</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>少昊（东方之帝）</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>20101</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_20</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>第20章现代译文</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>东海之外大壑，少昊之国。少昊孺帝颛顼于此，弃其琴瑟。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_21</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>颛顼（北方之帝）</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>21101</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_21</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>第21章现代译文</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>颛顼生老童，老童生重及黎……帝颛顼与九嫔葬焉（附禺之山）……颛顼生驩头，驩头生苗民。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_22</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>炎帝神农</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>22101</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_22</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>第22章现代译文</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>（北山经）是炎帝之少女，名曰女娃……（传世）炎帝神农氏，人身牛首，尝百草，教耕稼。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="n">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_23</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>伏羲（雷泽生）</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>23101</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_23</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>第23章现代译文</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>雷泽中有雷神，龙身而人头，鼓其腹。在吴西。（传世）华胥履雷泽大迹，而生伏羲。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_24</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>后稷（农神）</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>24101</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_24</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>第24章现代译文</t>
+        </is>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>帝俊生后稷，稷降以百谷……后稷是播百谷。后稷之葬，山水环之，爰有膏菽膏稻……百谷自生。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_25</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>太子长琴（乐祖）</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>25101</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_25</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>第25章现代译文</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>颛顼生老童，老童生祝融，祝融生太子长琴，是处榣山，始作乐风。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_26</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>相柳（九首蛇身）</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>26101</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_26</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>第26章现代译文</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>共工之臣曰相柳氏，九首，蛇身而青。不敢北射，畏共工之台。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_27</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>贰负杀窫窳</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>27101</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_27</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>第27章现代译文</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>贰负之臣曰危，危与贰负杀窫窳。帝乃梏之疏属之山，桎其右足，反缚两手与发，系之山上木。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="n">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_28</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>穷奇（是非颠倒）</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>28101</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_28</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>第28章现代译文</t>
+        </is>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>穷奇状如虎，有翼，食人从首始……为物，状如牛，猬毛，名曰穷奇，音如獆狗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_29</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>饕餮（狍鸮）</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>29101</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_29</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>第29章现代译文</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>（北山经）有兽焉，其状如羊身人面，其目在腋下，虎齿人爪，其音如婴儿，食人。（吕氏）周鼎著饕餮，有首无身，食人未咽。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_30</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>九凤与强良</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>30101&amp;30102</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_30</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>第30章现代译文</t>
+        </is>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>有神，九首人面鸟身，名曰九凤。又有神，衔蛇操蛇，其状虎首人身，四蹄长肘，名曰强良。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="n">
         <v>31</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_31</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>巴蛇吞象</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>31101</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_31</t>
+        </is>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>第31章现代译文</t>
+        </is>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>有黑蛇，青首，食象。巴蛇食象，三岁而出其骨，君子服之，无心腹之疾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="n">
         <v>32</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_32</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>嫦娥奔月</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>32101</t>
+        </is>
+      </c>
+      <c r="F35" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_32</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>第32章现代译文</t>
+        </is>
+      </c>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>（淮南子）羿请不死之药于西王母，姮娥（嫦娥）窃以奔月。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="n">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_33</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>不死之国与蓬莱仙山</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>33101</t>
+        </is>
+      </c>
+      <c r="F36" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_33</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>第33章现代译文</t>
+        </is>
+      </c>
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>不死民在其东，其为人黑色，寿，不死。蓬莱山在海中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_34</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>羽民与不死民（异形之民）</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>34101</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_34</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>第34章现代译文</t>
+        </is>
+      </c>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>羽民国在其东南，其为人长头，身生羽。不死民在其东，其为人黑色，寿，不死。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_35</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>欧丝之野（蚕女）</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>35101</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_35</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>第35章现代译文</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>欧丝之野在反踵东，一女子跪据树欧丝。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_36</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>雷神（雷泽）</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>36101</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_36</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>第36章现代译文</t>
+        </is>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>雷泽中有雷神，龙身而人头，鼓其腹。在吴西。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>53</v>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>myths_chapter_37</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>建木（天梯）</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>37101</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>definition_myths_info_37</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>第37章现代译文</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>有木……名曰建木。众帝所自上下。</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>